--- a/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,43</t>
+          <t>-2,5; 1,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,0</t>
+          <t>-0,83; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,46</t>
+          <t>-0,55; 0,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,44</t>
+          <t>-0,83; 0,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,84</t>
+          <t>-0,76; 1,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,67</t>
+          <t>-1,78; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,5</t>
+          <t>-0,37; 0,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,45</t>
+          <t>-0,26; 0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,29</t>
+          <t>-0,76; 0,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,42; 155,92</t>
+          <t>-90,03; 218,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,42</t>
+          <t>-2,52; 1,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,0</t>
+          <t>-0,71; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,35</t>
+          <t>-0,55; 0,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,48</t>
+          <t>-0,82; 0,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,89</t>
+          <t>-0,76; 1,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,69</t>
+          <t>-1,86; 0,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,48</t>
+          <t>-0,38; 0,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,52</t>
+          <t>-0,33; 0,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,32</t>
+          <t>-0,69; 0,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,03; 218,97</t>
+          <t>-89,38; 177,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,42</t>
+          <t>-2,53; 1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,0</t>
+          <t>-0,9; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,33</t>
+          <t>-0,55; 0,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,46</t>
+          <t>-0,92; 0,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,86</t>
+          <t>-0,76; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,69</t>
+          <t>-1,85; 0,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,48</t>
+          <t>-0,38; 0,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,47</t>
+          <t>-0,3; 0,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,3</t>
+          <t>-0,85; 0,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,38; 177,64</t>
+          <t>-89,42; 155,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,127 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-12,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.100207312109242</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.1242506159155632</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,53; 1,43</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.526021789764379</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.427432425536757</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-43,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-28,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,55; 0,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 0,44</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.1423110220358415</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.1200221180301028</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1466280955135008</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.437592853928001</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2876529668004762</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-52,53%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.9014676422645806</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.550342501851886</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.9168866179392335</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 1,84</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,3</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,85; 0,67</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4570688718911515</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.435623105267567</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +731,143 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-36,68%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.3695027143254792</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6674570851481565</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3868930105414466</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.9701780229195226</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.5252589651444866</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 0,5</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,3; 0,45</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,85; 0,29</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-89,42; 155,92</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.764754191451877</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.852496446510854</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.839285828362649</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.299138000870017</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6680899186876479</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01157328744142818</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.07355943843767067</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.1906743899946088</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.04216825494516258</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4071345311207708</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3667640239324016</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.375164961145935</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.2959676551510658</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.8520872983028357</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.8941683134472348</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5015467154130901</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4506162484667746</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2857973357851848</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>1.559219365753002</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +876,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
